--- a/DKS.xlsx
+++ b/DKS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9151F33D-54B1-4158-887F-8C68D3EAD73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71A68A1-874B-408C-9435-C801B15CB000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{AEDF7C68-C22C-401E-A9BD-35ACF1F87F21}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{AEDF7C68-C22C-401E-A9BD-35ACF1F87F21}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Dicks Sporting Goods</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>IR</t>
+  </si>
+  <si>
+    <t>DKS</t>
   </si>
 </sst>
 </file>
@@ -220,13 +223,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -288,24 +303,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -679,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>225.4</v>
+        <v>127.52</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -689,8 +706,8 @@
       <c r="J3" s="7">
         <v>88.534999999999997</v>
       </c>
-      <c r="K3" s="12" t="s">
-        <v>43</v>
+      <c r="K3" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -702,29 +719,32 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>19955.789000000001</v>
+        <v>11289.983199999999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="I5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>998.22799999999995</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>43</v>
+        <v>913.73599999999999</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="13" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>1905.81</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>43</v>
+        <v>1906.348</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -733,7 +753,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>20863.371000000003</v>
+        <v>12282.595199999998</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -836,6 +856,9 @@
       <c r="K3" s="2">
         <v>720</v>
       </c>
+      <c r="L3" s="2">
+        <v>723</v>
+      </c>
       <c r="R3" s="2">
         <v>722</v>
       </c>
@@ -853,6 +876,9 @@
       <c r="K4" s="2">
         <v>168</v>
       </c>
+      <c r="L4" s="2">
+        <v>169</v>
+      </c>
       <c r="R4" s="2">
         <v>131</v>
       </c>
@@ -905,7 +931,7 @@
       </c>
       <c r="L5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="M5" s="1">
         <f t="shared" si="0"/>
@@ -952,7 +978,9 @@
       <c r="K6" s="11">
         <v>2483</v>
       </c>
-      <c r="L6" s="1"/>
+      <c r="L6" s="12">
+        <v>2478</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -1004,13 +1032,17 @@
       <c r="G8" s="3">
         <v>3174.6770000000001</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>3646.616</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3">
         <v>3377.44</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <v>3849.8870000000002</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -1035,13 +1067,17 @@
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3">
         <v>1787.0640000000001</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3">
+        <v>1736.9280000000001</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1278,13 +1314,17 @@
       <c r="G14" s="1">
         <v>3174.6770000000001</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1">
+        <v>3646.616</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6">
         <v>5164.5039999999999</v>
       </c>
-      <c r="L14" s="6"/>
+      <c r="L14" s="6">
+        <v>5586.8149999999996</v>
+      </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -1335,13 +1375,17 @@
       <c r="G15" s="3">
         <v>2009.5909999999999</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>2295.3440000000001</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3">
         <v>3481.2420000000002</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>3643.5439999999999</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1408,7 +1452,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1351.2719999999999</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="2"/>
@@ -1424,7 +1468,7 @@
       </c>
       <c r="L16" s="3">
         <f t="shared" ref="L16:P16" si="3">+L14-L15</f>
-        <v>0</v>
+        <v>1943.2709999999997</v>
       </c>
       <c r="M16" s="3">
         <f t="shared" si="3"/>
@@ -1490,14 +1534,18 @@
       <c r="G17" s="3">
         <v>785.52800000000002</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>878.73699999999997</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3">
         <f>1163.928+53.815</f>
         <v>1217.7430000000002</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>1447.422</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -1550,13 +1598,19 @@
       <c r="G18" s="3">
         <v>13.442</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3">
+        <f>8.028+12.322</f>
+        <v>20.350000000000001</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3">
         <v>14.869</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <f>31.605+23.488</f>
+        <v>55.093000000000004</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -1623,7 +1677,7 @@
       </c>
       <c r="H19" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>452.18499999999995</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="5"/>
@@ -1639,7 +1693,7 @@
       </c>
       <c r="L19" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>440.75599999999969</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="5"/>
@@ -1705,13 +1759,17 @@
       <c r="G20" s="3">
         <v>12.138</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="3">
+        <v>16.117999999999999</v>
+      </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3">
         <v>17.541</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3">
+        <v>17.846</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -1763,13 +1821,17 @@
       <c r="G21" s="3">
         <v>-6.2560000000000002</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3">
+        <v>73.748999999999995</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3">
         <v>13.166</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="3">
+        <v>15.504</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1836,7 +1898,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>509.81599999999992</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -1852,7 +1914,7 @@
       </c>
       <c r="L22" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>438.4139999999997</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="8"/>
@@ -1918,13 +1980,17 @@
       <c r="G23" s="3">
         <v>83.433999999999997</v>
       </c>
-      <c r="H23" s="3"/>
+      <c r="H23" s="3">
+        <v>128.41399999999999</v>
+      </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3">
         <v>126.453</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <v>122.953</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1991,7 +2057,7 @@
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>381.40199999999993</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="10"/>
@@ -2007,7 +2073,7 @@
       </c>
       <c r="L24" s="3">
         <f t="shared" ref="L24:N24" si="11">+L22-L23</f>
-        <v>0</v>
+        <v>315.46099999999967</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="11"/>
@@ -2129,9 +2195,9 @@
         <f t="shared" si="13"/>
         <v>3.3310394373653001</v>
       </c>
-      <c r="H26" s="7" t="e">
+      <c r="H26" s="7">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>4.8189065915322109</v>
       </c>
       <c r="I26" s="7" t="e">
         <f t="shared" si="13"/>
@@ -2145,9 +2211,9 @@
         <f>+K24/K27</f>
         <v>3.6123792850285148</v>
       </c>
-      <c r="L26" s="7" t="e">
+      <c r="L26" s="7">
         <f t="shared" ref="L26:N26" si="14">+L24/L27</f>
-        <v>#DIV/0!</v>
+        <v>3.5513289578853717</v>
       </c>
       <c r="M26" s="7" t="e">
         <f t="shared" si="14"/>
@@ -2159,7 +2225,7 @@
       </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7" t="e">
-        <f t="shared" ref="J26:R26" si="15">+P24/P27</f>
+        <f t="shared" ref="P26:R26" si="15">+P24/P27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q26" s="7">
@@ -2187,13 +2253,17 @@
       <c r="G27" s="7">
         <v>79.340999999999994</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="7">
+        <v>79.147000000000006</v>
+      </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7">
         <v>88.534999999999997</v>
       </c>
-      <c r="L27" s="7"/>
+      <c r="L27" s="7">
+        <v>88.828999999999994</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
